--- a/feedback_forms/040_poverty_reduction_policy_awareness_survey--feedback_forms.xlsx
+++ b/feedback_forms/040_poverty_reduction_policy_awareness_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'high_school'}</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'some_college'}</t>
+          <t>some college</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'degree'}</t>
+          <t>degree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'degree'}</t>
+          <t>degree</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'some_university'}</t>
+          <t>some_university</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'some_university'}</t>
+          <t>some university</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_employed'}</t>
+          <t>not_employed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'not_employed'}</t>
+          <t>not employed</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'self_employed'}</t>
+          <t>self employed</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'student'}</t>
+          <t>student</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
     </row>
